--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/199.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/199.xlsx
@@ -426,13 +426,13 @@
         <v>-3.632357522530609</v>
       </c>
       <c r="E2">
-        <v>-18.38353703522775</v>
+        <v>-17.15374840591273</v>
       </c>
       <c r="F2">
-        <v>-3.629678305279171</v>
+        <v>-3.23176953824222</v>
       </c>
       <c r="G2">
-        <v>-10.69212966867219</v>
+        <v>-10.91914701848218</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.443891703841039</v>
       </c>
       <c r="E3">
-        <v>-19.82699718212069</v>
+        <v>-18.03979415872751</v>
       </c>
       <c r="F3">
-        <v>-3.87086410154347</v>
+        <v>-3.683941340366956</v>
       </c>
       <c r="G3">
-        <v>-8.750938322991905</v>
+        <v>-11.4330562447254</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.189966164604073</v>
       </c>
       <c r="E4">
-        <v>-19.43611741967462</v>
+        <v>-18.56406918001753</v>
       </c>
       <c r="F4">
-        <v>-3.575025937512071</v>
+        <v>-3.303366161233585</v>
       </c>
       <c r="G4">
-        <v>-9.641114223592073</v>
+        <v>-10.46620479889017</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.879549660021416</v>
       </c>
       <c r="E5">
-        <v>-18.34376797649239</v>
+        <v>-19.23936880946336</v>
       </c>
       <c r="F5">
-        <v>-3.207742741724021</v>
+        <v>-2.960388921778477</v>
       </c>
       <c r="G5">
-        <v>-10.12931706372286</v>
+        <v>-9.729432957488751</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.507549647910357</v>
       </c>
       <c r="E6">
-        <v>-20.13632818463664</v>
+        <v>-20.30511799632453</v>
       </c>
       <c r="F6">
-        <v>-3.527804025348083</v>
+        <v>-3.340516782514337</v>
       </c>
       <c r="G6">
-        <v>-9.729591863674635</v>
+        <v>-10.27816581225957</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.075932807378352</v>
       </c>
       <c r="E7">
-        <v>-20.77727028178627</v>
+        <v>-20.79284823237266</v>
       </c>
       <c r="F7">
-        <v>-3.098628530692464</v>
+        <v>-3.188133628564951</v>
       </c>
       <c r="G7">
-        <v>-8.261593344650073</v>
+        <v>-10.22163493663097</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.583688156873031</v>
       </c>
       <c r="E8">
-        <v>-21.56214086832169</v>
+        <v>-21.8827296572207</v>
       </c>
       <c r="F8">
-        <v>-3.67789425832652</v>
+        <v>-3.148084549741804</v>
       </c>
       <c r="G8">
-        <v>-7.974453177301387</v>
+        <v>-9.244507557441846</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.039144403980887</v>
       </c>
       <c r="E9">
-        <v>-24.11487789423753</v>
+        <v>-21.73097143627565</v>
       </c>
       <c r="F9">
-        <v>-4.251721753961196</v>
+        <v>-3.014930288313602</v>
       </c>
       <c r="G9">
-        <v>-6.058594126087601</v>
+        <v>-8.798421477661671</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.4476957146873997</v>
       </c>
       <c r="E10">
-        <v>-23.41698570796743</v>
+        <v>-23.73098103871128</v>
       </c>
       <c r="F10">
-        <v>-3.516310427634239</v>
+        <v>-3.40593461304822</v>
       </c>
       <c r="G10">
-        <v>-7.446970714347152</v>
+        <v>-8.519885418169551</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.1777603997956988</v>
       </c>
       <c r="E11">
-        <v>-22.41274678355245</v>
+        <v>-23.48849031254855</v>
       </c>
       <c r="F11">
-        <v>-3.953289971591632</v>
+        <v>-3.183894044197423</v>
       </c>
       <c r="G11">
-        <v>-6.685250601761783</v>
+        <v>-7.779134301029926</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.817434630067767</v>
       </c>
       <c r="E12">
-        <v>-24.29970303238659</v>
+        <v>-23.76326000143796</v>
       </c>
       <c r="F12">
-        <v>-3.766466614503454</v>
+        <v>-3.430665521858799</v>
       </c>
       <c r="G12">
-        <v>-6.836016156165733</v>
+        <v>-7.339530269415644</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.455005898663129</v>
       </c>
       <c r="E13">
-        <v>-23.2347146291587</v>
+        <v>-24.4289456805655</v>
       </c>
       <c r="F13">
-        <v>-3.939793381497819</v>
+        <v>-3.226201252560602</v>
       </c>
       <c r="G13">
-        <v>-6.42085719281343</v>
+        <v>-7.173734838263404</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.066306283946965</v>
       </c>
       <c r="E14">
-        <v>-26.59692996936764</v>
+        <v>-24.705544872954</v>
       </c>
       <c r="F14">
-        <v>-3.93344643045757</v>
+        <v>-2.71933649266603</v>
       </c>
       <c r="G14">
-        <v>-6.128443326420684</v>
+        <v>-6.244103855926202</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.62903586871901</v>
       </c>
       <c r="E15">
-        <v>-27.14800449983506</v>
+        <v>-25.24537520246037</v>
       </c>
       <c r="F15">
-        <v>-3.222644242932981</v>
+        <v>-3.163744007124325</v>
       </c>
       <c r="G15">
-        <v>-6.147469031634875</v>
+        <v>-5.552924847691624</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.129204316204417</v>
       </c>
       <c r="E16">
-        <v>-27.13802374312215</v>
+        <v>-26.28535284374389</v>
       </c>
       <c r="F16">
-        <v>-3.748751977594587</v>
+        <v>-3.14109147212737</v>
       </c>
       <c r="G16">
-        <v>-5.100909580850614</v>
+        <v>-5.866241498619328</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.552655793721469</v>
       </c>
       <c r="E17">
-        <v>-28.72017293497401</v>
+        <v>-27.36332891042577</v>
       </c>
       <c r="F17">
-        <v>-3.235435063999609</v>
+        <v>-2.715975806112872</v>
       </c>
       <c r="G17">
-        <v>-3.790214943670063</v>
+        <v>-5.817440746824931</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.89233439574374</v>
       </c>
       <c r="E18">
-        <v>-28.59350698850546</v>
+        <v>-28.25470014867359</v>
       </c>
       <c r="F18">
-        <v>-2.297742216480832</v>
+        <v>-2.391307971361842</v>
       </c>
       <c r="G18">
-        <v>-3.394512056452056</v>
+        <v>-5.409889417121873</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.146269812225517</v>
       </c>
       <c r="E19">
-        <v>-30.44688233833572</v>
+        <v>-29.35494725052519</v>
       </c>
       <c r="F19">
-        <v>-2.595942055977612</v>
+        <v>-2.491555337713833</v>
       </c>
       <c r="G19">
-        <v>-4.07989098890183</v>
+        <v>-4.539964123585426</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.312810693582015</v>
       </c>
       <c r="E20">
-        <v>-30.5835494196502</v>
+        <v>-28.98570000841376</v>
       </c>
       <c r="F20">
-        <v>-2.891284027934734</v>
+        <v>-2.095661988567893</v>
       </c>
       <c r="G20">
-        <v>-4.427197010881232</v>
+        <v>-4.944688247397947</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.393932853297966</v>
       </c>
       <c r="E21">
-        <v>-30.80070106950302</v>
+        <v>-29.8798041807252</v>
       </c>
       <c r="F21">
-        <v>-2.549984232470296</v>
+        <v>-1.922939101410168</v>
       </c>
       <c r="G21">
-        <v>-5.373185398727974</v>
+        <v>-4.467509523912937</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.391509451561164</v>
       </c>
       <c r="E22">
-        <v>-29.73430431085875</v>
+        <v>-30.96001504932986</v>
       </c>
       <c r="F22">
-        <v>-2.215761179727974</v>
+        <v>-2.100309129697598</v>
       </c>
       <c r="G22">
-        <v>-2.30922915449494</v>
+        <v>-4.657740091690537</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.306834573658239</v>
       </c>
       <c r="E23">
-        <v>-31.42666976734629</v>
+        <v>-30.77104635746379</v>
       </c>
       <c r="F23">
-        <v>-1.868748134286427</v>
+        <v>-1.815214062513106</v>
       </c>
       <c r="G23">
-        <v>-3.272359547144028</v>
+        <v>-3.833228861861813</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.141058261730595</v>
       </c>
       <c r="E24">
-        <v>-31.11697422267272</v>
+        <v>-31.56738304018663</v>
       </c>
       <c r="F24">
-        <v>-3.321791537374054</v>
+        <v>-1.486719998728546</v>
       </c>
       <c r="G24">
-        <v>-5.203437176201843</v>
+        <v>-4.035940186322466</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.897218089936468</v>
       </c>
       <c r="E25">
-        <v>-30.81843457371706</v>
+        <v>-31.62211191280633</v>
       </c>
       <c r="F25">
-        <v>-1.985237300305108</v>
+        <v>-1.641792033267419</v>
       </c>
       <c r="G25">
-        <v>-4.015080438879519</v>
+        <v>-4.339268921358189</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.578096442250047</v>
       </c>
       <c r="E26">
-        <v>-32.48144872592388</v>
+        <v>-31.45272434254942</v>
       </c>
       <c r="F26">
-        <v>-2.68648012800139</v>
+        <v>-1.332472189755458</v>
       </c>
       <c r="G26">
-        <v>-3.754394840935148</v>
+        <v>-5.048493713327334</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.188275264765462</v>
       </c>
       <c r="E27">
-        <v>-31.15289634273857</v>
+        <v>-30.90610130203154</v>
       </c>
       <c r="F27">
-        <v>-2.2351797683844</v>
+        <v>-1.656270238733548</v>
       </c>
       <c r="G27">
-        <v>-3.519021674184045</v>
+        <v>-4.446378311735769</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.737206865063453</v>
       </c>
       <c r="E28">
-        <v>-31.52112467819828</v>
+        <v>-30.18773135629877</v>
       </c>
       <c r="F28">
-        <v>-2.368282671033627</v>
+        <v>-1.907870269985842</v>
       </c>
       <c r="G28">
-        <v>-3.7571558359149</v>
+        <v>-4.714618574600756</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.233505142692182</v>
       </c>
       <c r="E29">
-        <v>-29.25459173804121</v>
+        <v>-30.98567338305732</v>
       </c>
       <c r="F29">
-        <v>-2.045858883576781</v>
+        <v>-1.389608002996151</v>
       </c>
       <c r="G29">
-        <v>-4.496559561020042</v>
+        <v>-4.860699707066637</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.690627389588872</v>
       </c>
       <c r="E30">
-        <v>-30.15130431138106</v>
+        <v>-30.141819422572</v>
       </c>
       <c r="F30">
-        <v>-2.997255413040069</v>
+        <v>-1.631460635019703</v>
       </c>
       <c r="G30">
-        <v>-2.949935585437789</v>
+        <v>-4.665615879528464</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.125760111765386</v>
       </c>
       <c r="E31">
-        <v>-30.13755360005677</v>
+        <v>-30.0089200316319</v>
       </c>
       <c r="F31">
-        <v>-2.698859250468826</v>
+        <v>-1.862531236928417</v>
       </c>
       <c r="G31">
-        <v>-4.045381862200468</v>
+        <v>-4.864420760252777</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.5527660661756304</v>
       </c>
       <c r="E32">
-        <v>-30.79831909217498</v>
+        <v>-29.43737906288682</v>
       </c>
       <c r="F32">
-        <v>-2.728871829839655</v>
+        <v>-1.649671464002848</v>
       </c>
       <c r="G32">
-        <v>-4.599265925830391</v>
+        <v>-5.549068062138373</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.007256397843154213</v>
       </c>
       <c r="E33">
-        <v>-30.56503475366985</v>
+        <v>-29.21575554495143</v>
       </c>
       <c r="F33">
-        <v>-2.236154756817495</v>
+        <v>-1.833117567189812</v>
       </c>
       <c r="G33">
-        <v>-5.964796439323431</v>
+        <v>-6.15180915683686</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.5352397772398233</v>
       </c>
       <c r="E34">
-        <v>-29.25024440299384</v>
+        <v>-29.31919041976063</v>
       </c>
       <c r="F34">
-        <v>-2.320470132911443</v>
+        <v>-2.243397173020171</v>
       </c>
       <c r="G34">
-        <v>-5.879612792052444</v>
+        <v>-6.084641498390587</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.016462706419516</v>
       </c>
       <c r="E35">
-        <v>-27.87455286962569</v>
+        <v>-28.57187446817082</v>
       </c>
       <c r="F35">
-        <v>-2.026672237793139</v>
+        <v>-1.872951270488232</v>
       </c>
       <c r="G35">
-        <v>-5.200378232123557</v>
+        <v>-6.438826834000594</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.432104260941041</v>
       </c>
       <c r="E36">
-        <v>-26.9793550708414</v>
+        <v>-27.92674353256409</v>
       </c>
       <c r="F36">
-        <v>-1.979929121987968</v>
+        <v>-1.803445446821534</v>
       </c>
       <c r="G36">
-        <v>-5.538888134605114</v>
+        <v>-6.123371570654521</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.770623048831353</v>
       </c>
       <c r="E37">
-        <v>-28.28042640951116</v>
+        <v>-28.270296213156</v>
       </c>
       <c r="F37">
-        <v>-2.318593880744102</v>
+        <v>-1.706725268870664</v>
       </c>
       <c r="G37">
-        <v>-6.32264985939095</v>
+        <v>-6.417334772359645</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.024304593318003</v>
       </c>
       <c r="E38">
-        <v>-26.15426257816985</v>
+        <v>-26.71625073099575</v>
       </c>
       <c r="F38">
-        <v>-2.079493913600052</v>
+        <v>-1.393377074678889</v>
       </c>
       <c r="G38">
-        <v>-4.441144339238181</v>
+        <v>-6.888243322593275</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.18882029760014</v>
       </c>
       <c r="E39">
-        <v>-25.97041559040645</v>
+        <v>-26.39698425650698</v>
       </c>
       <c r="F39">
-        <v>-2.043546910155568</v>
+        <v>-1.314507385890945</v>
       </c>
       <c r="G39">
-        <v>-5.190893519153545</v>
+        <v>-6.482671699122701</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.267895195568266</v>
       </c>
       <c r="E40">
-        <v>-25.76635349467281</v>
+        <v>-25.41635226709397</v>
       </c>
       <c r="F40">
-        <v>-2.167407717691761</v>
+        <v>-1.670935655232711</v>
       </c>
       <c r="G40">
-        <v>-6.371384400274561</v>
+        <v>-6.862113186651808</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.267913261007493</v>
       </c>
       <c r="E41">
-        <v>-26.0923039967969</v>
+        <v>-24.83216553468247</v>
       </c>
       <c r="F41">
-        <v>-1.371768282609461</v>
+        <v>-1.35918041155652</v>
       </c>
       <c r="G41">
-        <v>-6.597570803154186</v>
+        <v>-7.639637843641657</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.199237327122315</v>
       </c>
       <c r="E42">
-        <v>-24.76789290309161</v>
+        <v>-23.45801368247693</v>
       </c>
       <c r="F42">
-        <v>-1.852106233164185</v>
+        <v>-1.288199265545436</v>
       </c>
       <c r="G42">
-        <v>-7.236472986778133</v>
+        <v>-7.645855048164408</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.076137219679689</v>
       </c>
       <c r="E43">
-        <v>-24.60537955637834</v>
+        <v>-23.72769789505572</v>
       </c>
       <c r="F43">
-        <v>-1.580983238962713</v>
+        <v>-1.433697029642752</v>
       </c>
       <c r="G43">
-        <v>-6.583640027524933</v>
+        <v>-7.654863042576764</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.913959485238033</v>
       </c>
       <c r="E44">
-        <v>-23.0020416346446</v>
+        <v>-23.50732876442046</v>
       </c>
       <c r="F44">
-        <v>-1.708858314932872</v>
+        <v>-0.9026000381140855</v>
       </c>
       <c r="G44">
-        <v>-8.930002420665543</v>
+        <v>-8.382150171008172</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.727973571048367</v>
       </c>
       <c r="E45">
-        <v>-24.29092232128571</v>
+        <v>-22.14448451181206</v>
       </c>
       <c r="F45">
-        <v>-1.375449547347502</v>
+        <v>-1.107045254962018</v>
       </c>
       <c r="G45">
-        <v>-8.13351164828121</v>
+        <v>-7.938017313096168</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.534391249282332</v>
       </c>
       <c r="E46">
-        <v>-22.41343964007562</v>
+        <v>-22.24212293989144</v>
       </c>
       <c r="F46">
-        <v>-1.827466444767914</v>
+        <v>-1.118341701233994</v>
       </c>
       <c r="G46">
-        <v>-9.487438699659105</v>
+        <v>-8.229947839840181</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.348257967925198</v>
       </c>
       <c r="E47">
-        <v>-22.18748237251489</v>
+        <v>-21.18649489243742</v>
       </c>
       <c r="F47">
-        <v>-0.88487711753119</v>
+        <v>-1.336515451048522</v>
       </c>
       <c r="G47">
-        <v>-8.763909040414768</v>
+        <v>-8.976316952759948</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.180792015789356</v>
       </c>
       <c r="E48">
-        <v>-18.86013628216502</v>
+        <v>-21.1299251951336</v>
       </c>
       <c r="F48">
-        <v>-1.548952756598664</v>
+        <v>-1.194336955134224</v>
       </c>
       <c r="G48">
-        <v>-8.344456299498031</v>
+        <v>-8.38011749604706</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.043831394373369</v>
       </c>
       <c r="E49">
-        <v>-20.92402906742685</v>
+        <v>-20.79498114363027</v>
       </c>
       <c r="F49">
-        <v>-1.147269119307156</v>
+        <v>-0.9512036671059436</v>
       </c>
       <c r="G49">
-        <v>-8.65007593204693</v>
+        <v>-9.008608013949999</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.944478908967312</v>
       </c>
       <c r="E50">
-        <v>-20.17933057381347</v>
+        <v>-19.33593398920292</v>
       </c>
       <c r="F50">
-        <v>-1.598554568310896</v>
+        <v>-0.7023571291005554</v>
       </c>
       <c r="G50">
-        <v>-8.51330405363748</v>
+        <v>-8.462473937427509</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8859202686032434</v>
       </c>
       <c r="E51">
-        <v>-19.51169765086263</v>
+        <v>-18.93967439963574</v>
       </c>
       <c r="F51">
-        <v>-1.118905819435301</v>
+        <v>-1.034061944938367</v>
       </c>
       <c r="G51">
-        <v>-7.89163325954544</v>
+        <v>-8.553500697575311</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.8722897216500897</v>
       </c>
       <c r="E52">
-        <v>-19.97597944849904</v>
+        <v>-19.00449044810752</v>
       </c>
       <c r="F52">
-        <v>-0.8602572099525859</v>
+        <v>-0.9985779988720473</v>
       </c>
       <c r="G52">
-        <v>-8.976568554220933</v>
+        <v>-9.34251294758643</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.9007691856729605</v>
       </c>
       <c r="E53">
-        <v>-18.93847888249771</v>
+        <v>-18.52364349255106</v>
       </c>
       <c r="F53">
-        <v>-1.379791020905574</v>
+        <v>-0.6970746301729029</v>
       </c>
       <c r="G53">
-        <v>-8.762866218569899</v>
+        <v>-9.862136175430436</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.9689276528246814</v>
       </c>
       <c r="E54">
-        <v>-17.78984956434816</v>
+        <v>-18.34110523377588</v>
       </c>
       <c r="F54">
-        <v>-1.424838468637214</v>
+        <v>-1.066670627749569</v>
       </c>
       <c r="G54">
-        <v>-8.825475255808595</v>
+        <v>-9.639038511538951</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.074521373419862</v>
       </c>
       <c r="E55">
-        <v>-17.49394548726495</v>
+        <v>-18.13668086012162</v>
       </c>
       <c r="F55">
-        <v>-0.6395072375153513</v>
+        <v>-0.6428844914165649</v>
       </c>
       <c r="G55">
-        <v>-9.603324346261292</v>
+        <v>-9.172062889405975</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.209468293383673</v>
       </c>
       <c r="E56">
-        <v>-18.21896323284099</v>
+        <v>-17.93140060487992</v>
       </c>
       <c r="F56">
-        <v>-1.002925271001939</v>
+        <v>-0.6709288698383421</v>
       </c>
       <c r="G56">
-        <v>-9.607028846719738</v>
+        <v>-9.844931270262844</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.36848399292322</v>
       </c>
       <c r="E57">
-        <v>-16.24377872491541</v>
+        <v>-16.15177371850157</v>
       </c>
       <c r="F57">
-        <v>-1.446454716013267</v>
+        <v>-0.4532695361809524</v>
       </c>
       <c r="G57">
-        <v>-9.722619854768929</v>
+        <v>-10.36515370684946</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.543774694122176</v>
       </c>
       <c r="E58">
-        <v>-15.99896036311274</v>
+        <v>-16.38942350595011</v>
       </c>
       <c r="F58">
-        <v>-0.3185513170962661</v>
+        <v>-0.6679359784120276</v>
       </c>
       <c r="G58">
-        <v>-9.539199079165609</v>
+        <v>-9.876851550352496</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.724736484635945</v>
       </c>
       <c r="E59">
-        <v>-15.51217657813222</v>
+        <v>-16.84780017348051</v>
       </c>
       <c r="F59">
-        <v>-1.370799921115588</v>
+        <v>-0.8867417725548917</v>
       </c>
       <c r="G59">
-        <v>-9.479986661650205</v>
+        <v>-10.55834059179363</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.902790720034941</v>
       </c>
       <c r="E60">
-        <v>-16.45002807359476</v>
+        <v>-16.91642014011873</v>
       </c>
       <c r="F60">
-        <v>-0.6744635135460876</v>
+        <v>-0.8135107806778042</v>
       </c>
       <c r="G60">
-        <v>-10.07902987698133</v>
+        <v>-9.945048788461483</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.066157020299138</v>
       </c>
       <c r="E61">
-        <v>-17.27956752774184</v>
+        <v>-16.13135482920099</v>
       </c>
       <c r="F61">
-        <v>-0.3104432569576644</v>
+        <v>-0.5815596242199147</v>
       </c>
       <c r="G61">
-        <v>-10.28126448288432</v>
+        <v>-10.42986162996005</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.203815581794679</v>
       </c>
       <c r="E62">
-        <v>-14.14782887215328</v>
+        <v>-16.60613815806118</v>
       </c>
       <c r="F62">
-        <v>-1.20225697587239</v>
+        <v>-0.6841893752223566</v>
       </c>
       <c r="G62">
-        <v>-11.92063339174926</v>
+        <v>-10.63462218210951</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.307176215676721</v>
       </c>
       <c r="E63">
-        <v>-16.50829142017745</v>
+        <v>-15.81753158046943</v>
       </c>
       <c r="F63">
-        <v>-1.871075846688294</v>
+        <v>-0.4560901271874848</v>
       </c>
       <c r="G63">
-        <v>-12.10042911998708</v>
+        <v>-10.71948470646319</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.367033559478123</v>
       </c>
       <c r="E64">
-        <v>-15.50941420898754</v>
+        <v>-15.18632117396228</v>
       </c>
       <c r="F64">
-        <v>-0.8863748057954516</v>
+        <v>-0.8266901060563444</v>
       </c>
       <c r="G64">
-        <v>-10.19597158761054</v>
+        <v>-10.81868851409299</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.377919983964156</v>
       </c>
       <c r="E65">
-        <v>-16.02366771729859</v>
+        <v>-15.53626353137902</v>
       </c>
       <c r="F65">
-        <v>-0.6124850644686286</v>
+        <v>-0.8927681454102582</v>
       </c>
       <c r="G65">
-        <v>-10.0087635479103</v>
+        <v>-10.57493304603645</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.337485933596522</v>
       </c>
       <c r="E66">
-        <v>-14.32020523525525</v>
+        <v>-13.99547742111323</v>
       </c>
       <c r="F66">
-        <v>-1.137339479249798</v>
+        <v>-0.8773116380414222</v>
       </c>
       <c r="G66">
-        <v>-9.357430265786386</v>
+        <v>-9.836608558777115</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.245478361836104</v>
       </c>
       <c r="E67">
-        <v>-14.57836448148452</v>
+        <v>-14.37199286400697</v>
       </c>
       <c r="F67">
-        <v>-1.792220240146198</v>
+        <v>-0.9855560633000392</v>
       </c>
       <c r="G67">
-        <v>-11.27819223494383</v>
+        <v>-9.910744915583555</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.104734016250896</v>
       </c>
       <c r="E68">
-        <v>-14.49572435931855</v>
+        <v>-14.61376356280248</v>
       </c>
       <c r="F68">
-        <v>-1.329057659321119</v>
+        <v>-0.646606346157343</v>
       </c>
       <c r="G68">
-        <v>-11.37014925838817</v>
+        <v>-10.59896429610602</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.920556981277686</v>
       </c>
       <c r="E69">
-        <v>-13.46637051805702</v>
+        <v>-14.6853859077078</v>
       </c>
       <c r="F69">
-        <v>-1.074417519700551</v>
+        <v>-0.5998218119820325</v>
       </c>
       <c r="G69">
-        <v>-11.57357897123084</v>
+        <v>-11.16882836305401</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.698171329918793</v>
       </c>
       <c r="E70">
-        <v>-15.00774532994381</v>
+        <v>-14.26068750137244</v>
       </c>
       <c r="F70">
-        <v>-0.8424522809968134</v>
+        <v>-0.8264415958355045</v>
       </c>
       <c r="G70">
-        <v>-11.7346800488084</v>
+        <v>-10.07583188999039</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.444819768804091</v>
       </c>
       <c r="E71">
-        <v>-15.9885448728951</v>
+        <v>-14.26018031228358</v>
       </c>
       <c r="F71">
-        <v>-1.198294066217397</v>
+        <v>-0.9329522481200622</v>
       </c>
       <c r="G71">
-        <v>-10.35856572122631</v>
+        <v>-10.00406588379007</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.168823192451518</v>
       </c>
       <c r="E72">
-        <v>-15.32990097084948</v>
+        <v>-14.27162829457497</v>
       </c>
       <c r="F72">
-        <v>-1.522711734012781</v>
+        <v>-1.029965668131523</v>
       </c>
       <c r="G72">
-        <v>-9.584725701421668</v>
+        <v>-10.77785293486608</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.8753928780670516</v>
       </c>
       <c r="E73">
-        <v>-14.65999022547278</v>
+        <v>-15.35627480347015</v>
       </c>
       <c r="F73">
-        <v>-1.616710725045455</v>
+        <v>-1.010246382107881</v>
       </c>
       <c r="G73">
-        <v>-9.375466117884336</v>
+        <v>-10.00389042487649</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.5727766122749808</v>
       </c>
       <c r="E74">
-        <v>-14.53805653434225</v>
+        <v>-14.06157955620319</v>
       </c>
       <c r="F74">
-        <v>-1.169201803031078</v>
+        <v>-0.9931223711572098</v>
       </c>
       <c r="G74">
-        <v>-9.699402998902022</v>
+        <v>-9.315227431251756</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.2676998723932536</v>
       </c>
       <c r="E75">
-        <v>-15.05981372408401</v>
+        <v>-15.0201397633028</v>
       </c>
       <c r="F75">
-        <v>-1.76672640495764</v>
+        <v>-0.688038798543166</v>
       </c>
       <c r="G75">
-        <v>-10.02845467277788</v>
+        <v>-9.74764757904582</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.03610162301528957</v>
       </c>
       <c r="E76">
-        <v>-14.50777462865296</v>
+        <v>-15.0883249964363</v>
       </c>
       <c r="F76">
-        <v>-1.446342058046487</v>
+        <v>-0.6156212634556275</v>
       </c>
       <c r="G76">
-        <v>-9.241743251916555</v>
+        <v>-8.997289258751231</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3322238271473463</v>
       </c>
       <c r="E77">
-        <v>-15.91809087428376</v>
+        <v>-15.41763562627409</v>
       </c>
       <c r="F77">
-        <v>-1.371807215877393</v>
+        <v>-1.272015451596942</v>
       </c>
       <c r="G77">
-        <v>-9.557165409807235</v>
+        <v>-9.038965716545116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.6171266308350536</v>
       </c>
       <c r="E78">
-        <v>-15.80299517890481</v>
+        <v>-15.98327825762417</v>
       </c>
       <c r="F78">
-        <v>-1.655462580515819</v>
+        <v>-1.229419143010186</v>
       </c>
       <c r="G78">
-        <v>-9.549034709962784</v>
+        <v>-9.298439654822113</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.8877694596108925</v>
       </c>
       <c r="E79">
-        <v>-15.63923197336543</v>
+        <v>-16.38987635335087</v>
       </c>
       <c r="F79">
-        <v>-1.272696369602043</v>
+        <v>-1.361779000099102</v>
       </c>
       <c r="G79">
-        <v>-8.75695358423676</v>
+        <v>-8.719292818182012</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.139089817051161</v>
       </c>
       <c r="E80">
-        <v>-16.38950954695625</v>
+        <v>-16.9860635418827</v>
       </c>
       <c r="F80">
-        <v>-2.035876228005644</v>
+        <v>-0.845085660970313</v>
       </c>
       <c r="G80">
-        <v>-8.8221878840881</v>
+        <v>-8.906987508076531</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.368372144206261</v>
       </c>
       <c r="E81">
-        <v>-18.11669217585176</v>
+        <v>-17.98465545921012</v>
       </c>
       <c r="F81">
-        <v>-2.256928554544901</v>
+        <v>-1.1828491559922</v>
       </c>
       <c r="G81">
-        <v>-8.614384940588046</v>
+        <v>-8.444027577682691</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.571239396276274</v>
       </c>
       <c r="E82">
-        <v>-17.10710512363372</v>
+        <v>-18.22764884598771</v>
       </c>
       <c r="F82">
-        <v>-1.604526268917677</v>
+        <v>-1.418071535323745</v>
       </c>
       <c r="G82">
-        <v>-7.235963162765085</v>
+        <v>-8.358370522399587</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.742536771352026</v>
       </c>
       <c r="E83">
-        <v>-20.7318859152814</v>
+        <v>-19.39302898949163</v>
       </c>
       <c r="F83">
-        <v>-1.558368808866286</v>
+        <v>-1.224401721651429</v>
       </c>
       <c r="G83">
-        <v>-6.246560280716341</v>
+        <v>-7.374691573588244</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.879236123566443</v>
       </c>
       <c r="E84">
-        <v>-20.07063361220736</v>
+        <v>-19.64276074559263</v>
       </c>
       <c r="F84">
-        <v>-1.721790786825378</v>
+        <v>-1.476510370489042</v>
       </c>
       <c r="G84">
-        <v>-7.119898746703776</v>
+        <v>-7.544671534302123</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.976533696327471</v>
       </c>
       <c r="E85">
-        <v>-20.30432551337319</v>
+        <v>-20.95128595247902</v>
       </c>
       <c r="F85">
-        <v>-2.100232091529138</v>
+        <v>-1.482603012736632</v>
       </c>
       <c r="G85">
-        <v>-7.409237116290539</v>
+        <v>-7.120405260171284</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.030542470033335</v>
       </c>
       <c r="E86">
-        <v>-20.82523135000151</v>
+        <v>-21.46372354271299</v>
       </c>
       <c r="F86">
-        <v>-1.218888936585798</v>
+        <v>-1.610893929142997</v>
       </c>
       <c r="G86">
-        <v>-7.631162847061122</v>
+        <v>-6.518173989485845</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.039150732942462</v>
       </c>
       <c r="E87">
-        <v>-23.3236266878253</v>
+        <v>-22.86080758729338</v>
       </c>
       <c r="F87">
-        <v>-1.947346946933656</v>
+        <v>-1.697485658859838</v>
       </c>
       <c r="G87">
-        <v>-6.666797620925886</v>
+        <v>-6.336289307012747</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.00136901967132</v>
       </c>
       <c r="E88">
-        <v>-24.15226497564485</v>
+        <v>-24.55063030562561</v>
       </c>
       <c r="F88">
-        <v>-2.189414126114533</v>
+        <v>-1.600841690710025</v>
       </c>
       <c r="G88">
-        <v>-5.922239376416099</v>
+        <v>-5.916141351532763</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.91745811773327</v>
       </c>
       <c r="E89">
-        <v>-25.71868224879406</v>
+        <v>-25.7695958820623</v>
       </c>
       <c r="F89">
-        <v>-2.34023249404003</v>
+        <v>-1.966855827636987</v>
       </c>
       <c r="G89">
-        <v>-5.495291560398452</v>
+        <v>-6.356755099536522</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.789771301300175</v>
       </c>
       <c r="E90">
-        <v>-27.3955761738344</v>
+        <v>-25.83646785773357</v>
       </c>
       <c r="F90">
-        <v>-2.368275215727002</v>
+        <v>-2.189932684108685</v>
       </c>
       <c r="G90">
-        <v>-6.985282033440392</v>
+        <v>-6.632288494224523</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.622264418171565</v>
       </c>
       <c r="E91">
-        <v>-29.68694326544953</v>
+        <v>-28.30977544955487</v>
       </c>
       <c r="F91">
-        <v>-3.46358732754826</v>
+        <v>-2.126047333269982</v>
       </c>
       <c r="G91">
-        <v>-5.055535243689364</v>
+        <v>-6.261560362554778</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.418301019629437</v>
       </c>
       <c r="E92">
-        <v>-31.4537726842822</v>
+        <v>-30.22046995913722</v>
       </c>
       <c r="F92">
-        <v>-2.793434785213848</v>
+        <v>-2.275530372942166</v>
       </c>
       <c r="G92">
-        <v>-5.914466215489891</v>
+        <v>-6.388635653079703</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.183175949173639</v>
       </c>
       <c r="E93">
-        <v>-30.27151038967767</v>
+        <v>-30.9632234731643</v>
       </c>
       <c r="F93">
-        <v>-2.765623178032258</v>
+        <v>-2.403255514412419</v>
       </c>
       <c r="G93">
-        <v>-7.790681483870904</v>
+        <v>-5.962869701819575</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.9230607506036145</v>
       </c>
       <c r="E94">
-        <v>-33.33150896003671</v>
+        <v>-33.36056138503292</v>
       </c>
       <c r="F94">
-        <v>-3.876801010719334</v>
+        <v>-2.789205969622557</v>
       </c>
       <c r="G94">
-        <v>-7.292311958389019</v>
+        <v>-6.001874549363268</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.6427783689244471</v>
       </c>
       <c r="E95">
-        <v>-34.84368869999606</v>
+        <v>-34.36074506097404</v>
       </c>
       <c r="F95">
-        <v>-3.698067489686896</v>
+        <v>-3.211567314022746</v>
       </c>
       <c r="G95">
-        <v>-5.833390955233139</v>
+        <v>-6.683525807535823</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3471516154665369</v>
       </c>
       <c r="E96">
-        <v>-38.41860420010827</v>
+        <v>-36.91503988194852</v>
       </c>
       <c r="F96">
-        <v>-3.778277476932569</v>
+        <v>-3.185244283063986</v>
       </c>
       <c r="G96">
-        <v>-7.510089575598896</v>
+        <v>-6.643031214499458</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.04530621169074254</v>
       </c>
       <c r="E97">
-        <v>-38.4368675357812</v>
+        <v>-39.63055743454408</v>
       </c>
       <c r="F97">
-        <v>-4.8022704688424</v>
+        <v>-3.563172828345413</v>
       </c>
       <c r="G97">
-        <v>-7.188506492459632</v>
+        <v>-6.777697585945932</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.2660719608724753</v>
       </c>
       <c r="E98">
-        <v>-40.48002217432492</v>
+        <v>-41.5520953751378</v>
       </c>
       <c r="F98">
-        <v>-4.032107473233199</v>
+        <v>-3.928058728869762</v>
       </c>
       <c r="G98">
-        <v>-7.420502902760679</v>
+        <v>-7.517435676150539</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.5715382485745067</v>
       </c>
       <c r="E99">
-        <v>-42.6878208066025</v>
+        <v>-42.82446750978395</v>
       </c>
       <c r="F99">
-        <v>-5.384923390786502</v>
+        <v>-4.334446664641768</v>
       </c>
       <c r="G99">
-        <v>-7.579654069015602</v>
+        <v>-6.021072402945502</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.8873427036089276</v>
       </c>
       <c r="E100">
-        <v>-45.94555519450647</v>
+        <v>-45.78978248135362</v>
       </c>
       <c r="F100">
-        <v>-5.377372821909986</v>
+        <v>-4.710674571645248</v>
       </c>
       <c r="G100">
-        <v>-7.368252562514361</v>
+        <v>-6.979763354026427</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.185360598570711</v>
       </c>
       <c r="E101">
-        <v>-46.71716640914742</v>
+        <v>-47.13036928421431</v>
       </c>
       <c r="F101">
-        <v>-5.722406069258841</v>
+        <v>-5.249794301470028</v>
       </c>
       <c r="G101">
-        <v>-5.906491111285787</v>
+        <v>-7.100310248747909</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.511510095841234</v>
       </c>
       <c r="E102">
-        <v>-50.27125432517986</v>
+        <v>-50.95189302548073</v>
       </c>
       <c r="F102">
-        <v>-5.715589433901203</v>
+        <v>-5.279682625730437</v>
       </c>
       <c r="G102">
-        <v>-8.410796321559486</v>
+        <v>-7.300402931686999</v>
       </c>
     </row>
   </sheetData>
